--- a/Config/Excel/Skill@技能配置/GlobalAttribute@属性字段@cs.xlsx
+++ b/Config/Excel/Skill@技能配置/GlobalAttribute@属性字段@cs.xlsx
@@ -1213,9 +1213,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6"/>
       <c r="J6" s="3"/>
-      <c r="K6"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12">
@@ -1237,9 +1235,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7"/>
       <c r="J7" s="3"/>
-      <c r="K7"/>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12">
